--- a/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
@@ -36,12 +36,12 @@
     <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
     <t xml:space="preserve">El Tabo</t>
   </si>
   <si>
-    <t xml:space="preserve">El Quisco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Algarrobo</t>
   </si>
   <si>
@@ -63,39 +63,39 @@
     <t xml:space="preserve">Papudo</t>
   </si>
   <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zapallar</t>
   </si>
   <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
     <t xml:space="preserve">Putaendo</t>
   </si>
   <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santo Domingo</t>
   </si>
   <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
     <t xml:space="preserve">Concón</t>
   </si>
   <si>
     <t xml:space="preserve">San Antonio</t>
   </si>
   <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
     <t xml:space="preserve">Los Andes</t>
   </si>
   <si>
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
-    <t xml:space="preserve">Puchuncaví</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
@@ -108,24 +108,24 @@
     <t xml:space="preserve">Catemu</t>
   </si>
   <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hijuelas</t>
   </si>
   <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casablanca</t>
-  </si>
-  <si>
     <t xml:space="preserve">Santa María</t>
   </si>
   <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rinconada</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -583,13 +583,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5605</v>
+        <v>5604</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>180.19</v>
+        <v>192.07</v>
       </c>
     </row>
     <row r="3">
@@ -600,13 +600,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5604</v>
+        <v>5605</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>178.53</v>
+        <v>191.91</v>
       </c>
     </row>
     <row r="4">
@@ -623,7 +623,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>169.04</v>
+        <v>182.87</v>
       </c>
     </row>
     <row r="5">
@@ -640,7 +640,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>153.65</v>
+        <v>165.13</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>144.79</v>
+        <v>156.11</v>
       </c>
     </row>
     <row r="7">
@@ -674,7 +674,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>142.18</v>
+        <v>152.81</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +691,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>140.55</v>
+        <v>151.16</v>
       </c>
     </row>
     <row r="9">
@@ -708,7 +708,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>138.49</v>
+        <v>149.03</v>
       </c>
     </row>
     <row r="10">
@@ -725,7 +725,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>137.65</v>
+        <v>148.02</v>
       </c>
     </row>
     <row r="11">
@@ -742,7 +742,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>134.27</v>
+        <v>144.39</v>
       </c>
     </row>
     <row r="12">
@@ -753,13 +753,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5405</v>
+        <v>5506</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>130.16</v>
+        <v>139.2</v>
       </c>
     </row>
     <row r="13">
@@ -770,13 +770,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5506</v>
+        <v>5501</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>128.94</v>
+        <v>138.59</v>
       </c>
     </row>
     <row r="14">
@@ -787,13 +787,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5501</v>
+        <v>5405</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>128.49</v>
+        <v>138.42</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +810,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>125.08</v>
+        <v>133.84</v>
       </c>
     </row>
     <row r="16">
@@ -821,13 +821,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5606</v>
+        <v>5401</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>124.55</v>
+        <v>132.99</v>
       </c>
     </row>
     <row r="17">
@@ -838,13 +838,13 @@
         <v>20</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5401</v>
+        <v>5606</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>124.5</v>
+        <v>132.71</v>
       </c>
     </row>
     <row r="18">
@@ -861,7 +861,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>120.98</v>
+        <v>130.41</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>119.61</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -889,13 +889,13 @@
         <v>23</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5301</v>
+        <v>5105</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>119.2</v>
+        <v>128.29</v>
       </c>
     </row>
     <row r="21">
@@ -906,13 +906,13 @@
         <v>24</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5802</v>
+        <v>5301</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>119.1</v>
+        <v>128.03</v>
       </c>
     </row>
     <row r="22">
@@ -923,13 +923,13 @@
         <v>25</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5105</v>
+        <v>5802</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>118.92</v>
+        <v>127.73</v>
       </c>
     </row>
     <row r="23">
@@ -946,7 +946,7 @@
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>118.83</v>
+        <v>127.66</v>
       </c>
     </row>
     <row r="24">
@@ -963,7 +963,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>117.54</v>
+        <v>127.24</v>
       </c>
     </row>
     <row r="25">
@@ -980,7 +980,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>116.32</v>
+        <v>125.64</v>
       </c>
     </row>
     <row r="26">
@@ -997,7 +997,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>115.34</v>
+        <v>124.74</v>
       </c>
     </row>
     <row r="27">
@@ -1008,13 +1008,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>5503</v>
+        <v>5102</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>111.4</v>
+        <v>119.42</v>
       </c>
     </row>
     <row r="28">
@@ -1031,7 +1031,7 @@
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>111.07</v>
+        <v>119.3</v>
       </c>
     </row>
     <row r="29">
@@ -1042,13 +1042,13 @@
         <v>32</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5102</v>
+        <v>5503</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>110.95</v>
+        <v>119.04</v>
       </c>
     </row>
     <row r="30">
@@ -1065,7 +1065,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>109.08</v>
+        <v>116.79</v>
       </c>
     </row>
     <row r="31">
@@ -1076,13 +1076,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5701</v>
+        <v>5304</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>103.07</v>
+        <v>111.23</v>
       </c>
     </row>
     <row r="32">
@@ -1093,13 +1093,13 @@
         <v>35</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>5304</v>
+        <v>5701</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>103.03</v>
+        <v>110.48</v>
       </c>
     </row>
     <row r="33">
@@ -1116,7 +1116,7 @@
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>93.48</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="34">
@@ -1133,7 +1133,7 @@
         <v>2021</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>90.36</v>
+        <v>96.4</v>
       </c>
     </row>
     <row r="35">
@@ -1150,7 +1150,7 @@
         <v>2021</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>83.07</v>
+        <v>88.94</v>
       </c>
     </row>
     <row r="36">
@@ -1167,7 +1167,7 @@
         <v>2021</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>78.47</v>
+        <v>84.54</v>
       </c>
     </row>
     <row r="37">
@@ -1184,7 +1184,7 @@
         <v>2021</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>75.35</v>
+        <v>78.92</v>
       </c>
     </row>
     <row r="38">
@@ -1201,7 +1201,7 @@
         <v>2021</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>57.84</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="39">
@@ -1218,7 +1218,7 @@
         <v>2021</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>53.7</v>
+        <v>57.33</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:25</t>
+    <t xml:space="preserve">2026-10-04 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:42</t>
+    <t xml:space="preserve">2026-10-05 16:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
